--- a/affiliate_data/เครื่องใช้ไฟฟ้าภายในบ้าน.xlsx
+++ b/affiliate_data/เครื่องใช้ไฟฟ้าภายในบ้าน.xlsx
@@ -442,37 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Sony BRAVIA 3 ทีวี 55 นิ้ว รุ่น K-55S30 4K Ultra HD Smart TV (Google TV) | 4K HDR Processor X1™</v>
+        <v>เครื่องปั่นผลไม้ Silver Crest 2in1 4500W 2.5L สมูทตี้ น้ำผลไม้ มิลค์เชค ปั่นน้ำแข็ง 6 ใบมีด พกพา</v>
       </c>
       <c r="C2" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-monb6x2bpm9ua9.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mm9pizydk5xc4b.webp</v>
       </c>
       <c r="D2" t="str">
-        <v>22490.00</v>
+        <v>358.00</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G2" t="str">
-        <v>ขายได้ 672 ชิ้น</v>
+        <v>ขายได้ 1พัน+ ชิ้น</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>https://shopee.co.th/product/0/28700107209</v>
+        <v>https://shopee.co.th/product/0/55957723567</v>
       </c>
       <c r="J2" t="str">
-        <v>https://s.shopee.co.th/4ftTK2w2lA</v>
+        <v>https://s.shopee.co.th/60P0xz4s5m</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -480,37 +480,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio สี Midnight Black เครื่องดริปกาแฟ รวม การบด ชั่ง และชง ในเครื่องเดียว</v>
+        <v>Candy เครื่องซักอบผ้าฝาหน้า ซักอบ 11/7kg 2in1 ประหยัดไฟ สะอาด ฆ่าเชื้อและไรฝุ่น รับประกันมอเตอร์ 12 ปี CWDE110CPG2C2IU1</v>
       </c>
       <c r="C3" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mky2xiag4h6u10.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-moz9y245klq8b9.webp</v>
       </c>
       <c r="D3" t="str">
-        <v>24000.00</v>
+        <v>10950.00</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="G3" t="str">
-        <v>ขายได้ 347 ชิ้น</v>
+        <v>ขายได้ 111 ชิ้น</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://shopee.co.th/product/0/27772049148</v>
+        <v>https://shopee.co.th/product/0/51307674655</v>
       </c>
       <c r="J3" t="str">
-        <v>https://s.shopee.co.th/50WJif4k6d</v>
+        <v>https://s.shopee.co.th/6VLHYuGAQD</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -518,37 +518,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>MASARU พัดลมไร้สาย SCFP-910 พัดลม 10นิ้ว พัดลมพกพาไร้สาย พัดลม แบตเตอรี่ แบตลิเธียม 20V</v>
+        <v>Toshiba TV 55E330RP ทีวี 55 นิ้ว 4K Ultra HD Wifi HDR10 Voice Control Smart TV</v>
       </c>
       <c r="C4" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134211-81zto-ml7l2x3b7wn7af.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mp3ebq6i0nb522.webp</v>
       </c>
       <c r="D4" t="str">
-        <v>784.00</v>
+        <v>11040.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G4" t="str">
-        <v>ขายได้ 150 ชิ้น</v>
+        <v>ขายได้ 7พัน+ ชิ้น</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>https://shopee.co.th/product/0/40556240552</v>
+        <v>https://shopee.co.th/product/0/21820153434</v>
       </c>
       <c r="J4" t="str">
-        <v>https://s.shopee.co.th/BR3xmVwTk</v>
+        <v>https://s.shopee.co.th/6py7xWJIX5</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -556,37 +556,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Hysure™ Q9 เครื่องดูดความชื้น เครื่องฟอกอากาศ PM2.5 ปิดอัตโนมัติ WiFi กรองฝุ่นอย่างมีประสิทธิภาพ</v>
+        <v>Airdog X8proUltra (D)เครื่องฟอกอากาศ ฝุ่นPM 2.5 ฆ่าเชื้อไวรัส ขนสัตว์ ฟอร์มาลดีไฮด์พื้นที่ 60-120 ตร.ม</v>
       </c>
       <c r="C5" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-7ras8-m8r3p8o2ot5e08.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mp1pzvpga5u7af.webp</v>
       </c>
       <c r="D5" t="str">
-        <v>2559.00</v>
+        <v>60900.00</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G5" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 90 ชิ้น</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>https://shopee.co.th/product/0/26401990656</v>
+        <v>https://shopee.co.th/product/0/27801066308</v>
       </c>
       <c r="J5" t="str">
-        <v>https://s.shopee.co.th/2g8OwNTuzQ</v>
+        <v>https://s.shopee.co.th/AUrQKGE8ej</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -594,37 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>ชุดนอนนา 1000W+ แผงโซล่า 100W+ แบต 12A รุ่น ECON INVERTER แผงจ่ายไฟ พลังแสงอาทิตย์ อุปกรณ์ครบ ไฟมาก ติดตั้งสดวก พร้อมใช้</v>
+        <v>BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX บด ชง ตีฟองในเครื่องเดียว</v>
       </c>
       <c r="C6" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mom2odud9jin5a.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lulivn98e2we52.webp</v>
       </c>
       <c r="D6" t="str">
-        <v>4467.00</v>
+        <v>18462.00</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G6" t="str">
-        <v>ขายได้ 329 ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>https://shopee.co.th/product/0/22248309313</v>
+        <v>https://shopee.co.th/product/0/22478097184</v>
       </c>
       <c r="J6" t="str">
-        <v>https://s.shopee.co.th/AKXq4T9fWP</v>
+        <v>https://s.shopee.co.th/gNUcC2qDR</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>5.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -632,31 +632,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX บด ชง ตีฟองในเครื่องเดียว</v>
+        <v>Candy เครื่องซักผ้าฝาหน้า 11 kg Inverter ประหยัดไฟ ซักเร็ว ลดแบคทีเรีย ลดกลิ่นอับ รับประกันมอเตอร์ 12ปี CFLE110CPG2C2IU1</v>
       </c>
       <c r="C7" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lulivn98e2we52.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-moz9ye8l0etobc.webp</v>
       </c>
       <c r="D7" t="str">
-        <v>22900.00</v>
+        <v>9990.00</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G7" t="str">
-        <v>ขายได้ 222 ชิ้น</v>
+        <v>ขายได้ 155 ชิ้น</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>https://shopee.co.th/product/0/22478097184</v>
+        <v>https://shopee.co.th/product/0/48857694304</v>
       </c>
       <c r="J7" t="str">
-        <v>https://s.shopee.co.th/5ApjuybejY</v>
+        <v>https://s.shopee.co.th/5fmAZNmYYs</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -670,37 +670,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>MITSUBISHI HEAVY DUTY แอร์ติดผนัง Standard Inverter (YYP) ขนาด 9,492-18,600 BTU (เครื่องเปล่าและบริการติดตั้ง) ผ่อน 0 %</v>
+        <v>[Pre-Order till 07/07/26] Toshiba TV 85E450RP ทีวี 85 นิ้ว 4K Ultra HD Quantum Dot HDR10+ Dolby Atmos Smart TV</v>
       </c>
       <c r="C8" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-23020-ig02bkz1bxnvac.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mp3e9p3e0nbic1.webp</v>
       </c>
       <c r="D8" t="str">
-        <v>13899.00</v>
+        <v>32490.00</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G8" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 53 ชิ้น</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>https://shopee.co.th/product/0/23827201056</v>
+        <v>https://shopee.co.th/product/0/29351430127</v>
       </c>
       <c r="J8" t="str">
-        <v>https://s.shopee.co.th/5q5QiCiXJ2</v>
+        <v>https://s.shopee.co.th/6py7xWqdi5</v>
       </c>
       <c r="K8" t="str">
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -708,31 +708,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>ถูกสุด ชุดนอนนาเลือกเองได้ 500w-1000W ชุดคอนโทรลชาร์จ30A แผง20W โซล่าเซลล์แสงอาทิตย์ 12V to 220V</v>
+        <v>[Flash Sale] AirdogX3Pro(D) เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ฆ่าเชื้อไวรัส ฟอร์มาลดีไฮด์พื้นที่30ตรม</v>
       </c>
       <c r="C9" t="str">
-        <v>https://down-bs-th.img.susercontent.com/c0e3f2ed5c06ef63871b7599081d4ea8.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mojkshj50veq04.webp</v>
       </c>
       <c r="D9" t="str">
-        <v>599.00</v>
+        <v>19800.00</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>24</v>
       </c>
       <c r="G9" t="str">
-        <v>ขายได้ 189 ชิ้น</v>
+        <v>ขายได้ 1พัน+ ชิ้น</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://shopee.co.th/product/0/14672573092</v>
+        <v>https://shopee.co.th/product/0/25015612928</v>
       </c>
       <c r="J9" t="str">
-        <v>https://s.shopee.co.th/9pbZTYbpho</v>
+        <v>https://s.shopee.co.th/W44PtO6Dz</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -746,37 +746,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Toshiba TV 55E330RP ทีวี 55 นิ้ว 4K Ultra HD Wifi HDR10 Voice Control Smart TV</v>
+        <v>xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio สี Midnight Black เครื่องดริปกาแฟ รวม การบด ชั่ง และชง ในเครื่องเดียว</v>
       </c>
       <c r="C10" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mgn5hdwg1xje1b.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mky2xiag4h6u10.webp</v>
       </c>
       <c r="D10" t="str">
-        <v>11590.00</v>
+        <v>26877.00</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="G10" t="str">
-        <v>ขายได้ 6พัน+ ชิ้น</v>
+        <v>ขายได้ 354 ชิ้น</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>https://shopee.co.th/product/0/21820153434</v>
+        <v>https://shopee.co.th/product/0/27772049148</v>
       </c>
       <c r="J10" t="str">
-        <v>https://s.shopee.co.th/7pqV5sp5Gj</v>
+        <v>https://s.shopee.co.th/7AayM9459y</v>
       </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -784,31 +784,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>TYPHOON S70 V4 ใหม่ เครื่องบดกาแฟออโต้ รุ่นใหม่2026 มีพัดลมระบาย ประกันศูนย์ไทย1ปี</v>
+        <v>TV Direct - SANSHIRO พัดลมอุตสาหกรรม 20" FS-20 5 ใบพัด</v>
       </c>
       <c r="C11" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mk4tghu2pz44a4.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-ma3vs5aezunic4.webp</v>
       </c>
       <c r="D11" t="str">
-        <v>16500.00</v>
+        <v>1760.00</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>61</v>
       </c>
       <c r="G11" t="str">
-        <v>ขายได้ 669 ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://shopee.co.th/product/0/9147151195</v>
+        <v>https://shopee.co.th/product/0/28481166419</v>
       </c>
       <c r="J11" t="str">
-        <v>https://s.shopee.co.th/LkUA6PCKb</v>
+        <v>https://s.shopee.co.th/4qD3ZrL96T</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -822,19 +822,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>MITSUBISHI HEAVY DUTY แอร์ติดผนัง รุ่น Deluxe Inverter (YYS) ขนาด 9,633 - 24,215 BTU (ติดตั้งต่างจังหวัด) ผ่อน 0 %</v>
+        <v>Toshiba TV 55Z570 ทีวี 55 นิ้ว 4K Quantum Dot Voice Control HDR10+ Dolby Vision Atmos Smart TV</v>
       </c>
       <c r="C12" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lkkqyzo9mv6if7.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mp3eao4sruoc12.webp</v>
       </c>
       <c r="D12" t="str">
-        <v>18800.00</v>
+        <v>15876.00</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G12" t="str">
         <v>ขายได้ 1พัน+ ชิ้น</v>
@@ -843,16 +843,16 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>https://shopee.co.th/product/0/22351756944</v>
+        <v>https://shopee.co.th/product/0/19211532551</v>
       </c>
       <c r="J12" t="str">
-        <v>https://s.shopee.co.th/4qCtWNH8oU</v>
+        <v>https://s.shopee.co.th/6VLHYvNbH5</v>
       </c>
       <c r="K12" t="str">
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -860,37 +860,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>ANKER eufy เครื่องดูดฝุ่นหุ่นยนต์ eufy Omni C20,7000 Pa ดูดทรงพลัง,ตัวบางเฉียบ 85 มม., การเปล่าด้วยตนเอง, ซักซับอัตโนมัติและอบแห้งอัตโนมัติสําหรับทําความสะอาดแบบแฮนด์ฟรี, สถานีออลอินวัน</v>
+        <v>Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไวรัสรุ่นMTK-AP05(42 ตร.ม)HEPA13กรองฝุ่นและขนสัตว์เลี้ยง</v>
       </c>
       <c r="C13" t="str">
-        <v>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mojw0ztqfbwv8f.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-matogng9t2d270.webp</v>
       </c>
       <c r="D13" t="str">
-        <v>9999.00</v>
+        <v>6390.00</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G13" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 180 ชิ้น</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>https://shopee.co.th/product/0/43913177803</v>
+        <v>https://shopee.co.th/product/0/9904114242</v>
       </c>
       <c r="J13" t="str">
-        <v>https://s.shopee.co.th/5VSaJbMmfK</v>
+        <v>https://s.shopee.co.th/4LGmywe1sM</v>
       </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -898,37 +898,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>ABL 43 นิ้ว LED Android TV ดิจิตอลทีวี สมาร์ททีวี HD Ready ทีวี43นิ้ว</v>
+        <v>รุ่นใหม่ล่าสุด 2026 เครื่องทำน้ำแข็ง อัตโนมัติ ice maker ทำน้ำแข็งเร็ว ไม่ละลายใน 5 ชั่วโมง เครื่องทำน้ำแข็งขนาดเล็ก</v>
       </c>
       <c r="C14" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-m02vru4kzg7sce.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mnxxrt37bfuw22.webp</v>
       </c>
       <c r="D14" t="str">
-        <v>4299.00</v>
+        <v>2890.00</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="G14" t="str">
-        <v>ขายได้ 317 ชิ้น</v>
+        <v>ขายได้ 749 ชิ้น</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>https://shopee.co.th/product/0/11774699251</v>
+        <v>https://shopee.co.th/product/0/44455601920</v>
       </c>
       <c r="J14" t="str">
-        <v>https://s.shopee.co.th/AUrGGnCH2K</v>
+        <v>https://s.shopee.co.th/W44Pu19Ad</v>
       </c>
       <c r="K14" t="str">
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -936,37 +936,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>kawu เครื่องนึ่งไฟฟ้าอเนกประสงค์ 3ชั้น หม้อนึ่งไฟฟ้า 24ลิตรความจุมาก หม้อนึ่งไฟฟ้า ไก่นึ่งได้ทั้งตัว</v>
+        <v>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2</v>
       </c>
       <c r="C15" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-miva3n0wouf766.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mozm7fobwdn34f.webp</v>
       </c>
       <c r="D15" t="str">
-        <v>898.00</v>
+        <v>10590.00</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G15" t="str">
-        <v>ขายได้ 8พัน+ ชิ้น</v>
+        <v>ขายได้ 100พัน+ ชิ้น</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>https://shopee.co.th/product/0/26730715093</v>
+        <v>https://shopee.co.th/product/0/13181175093</v>
       </c>
       <c r="J15" t="str">
-        <v>https://s.shopee.co.th/6VL7VRaqof</v>
+        <v>https://s.shopee.co.th/1Vwbbk7276</v>
       </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -974,37 +974,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>MITSUBISHI HEAVY DUTY แอร์ติดผนัง Standard Inverter (YYM) ขนาด 9,575 - 24,225 BTU (เครื่องเปล่าและบริการติดตั้ง)ผ่อน 0 %</v>
+        <v>Toshiba TV 75C350RP ทีวี 75 นิ้ว 4K Ultra HD HDR10 Dolby Vision Atmos LED Wi-Fi Smart TV</v>
       </c>
       <c r="C16" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lmh6vas1pds7a8.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mp3egibrdtz433.webp</v>
       </c>
       <c r="D16" t="str">
-        <v>17300.00</v>
+        <v>23790.00</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G16" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 314 ชิ้น</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>https://shopee.co.th/product/0/23982320488</v>
+        <v>https://shopee.co.th/product/0/20923611494</v>
       </c>
       <c r="J16" t="str">
-        <v>https://s.shopee.co.th/5ApjuzoS2P</v>
+        <v>https://s.shopee.co.th/30lPOVAjzi</v>
       </c>
       <c r="K16" t="str">
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1012,37 +1012,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>ปลั๊กไฟสนาม บล็อกยาง แข็งแรง ทนทาน สาย VCT 2x2.5 ขยายได้ 0-30ม.</v>
+        <v>PETX FRESH BOX V.1 เครื่องกำจัดกลิ่นสัตว์เลี้ยง ดับกลิ่นฉี่แมว ฉี่สุนัข กรองขนสัตว์ ฟอกอากาศ PM2.5</v>
       </c>
       <c r="C17" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mmjtmbb71yiu17.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mkkusff6q8lh90.webp</v>
       </c>
       <c r="D17" t="str">
-        <v>95.00</v>
+        <v>3990.00</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G17" t="str">
-        <v>ขายได้ 346 ชิ้น</v>
+        <v>ขายได้ 2พัน+ ชิ้น</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>https://shopee.co.th/product/0/55708040988</v>
+        <v>https://shopee.co.th/product/0/3359706931</v>
       </c>
       <c r="J17" t="str">
-        <v>https://s.shopee.co.th/8KmlgolTE0</v>
+        <v>https://s.shopee.co.th/8fPm8usC2H</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1050,37 +1050,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>SMART TV 32 นิ้ว LG - SAMSUNG พร้อมขาตั้งติดล้อ รับประกันศูนย์</v>
+        <v>TCL ตู้เย็น Side by Side ขนาด 17.5Q/505L ระบบ Inverter ละลายน้ำแข็งอัตโนมัติ รุ่น P505SBN/RT50MPSBG</v>
       </c>
       <c r="C18" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-ml50a7qovdvl83.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mozm4emq56312d.webp</v>
       </c>
       <c r="D18" t="str">
-        <v>19900.00</v>
+        <v>15490.00</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="G18" t="str">
-        <v>ขายได้ 10 ชิ้น</v>
+        <v>ขายได้ 8พัน+ ชิ้น</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>https://shopee.co.th/product/0/28442398566</v>
+        <v>https://shopee.co.th/product/0/13622572843</v>
       </c>
       <c r="J18" t="str">
-        <v>https://s.shopee.co.th/70HO6N0ijx</v>
+        <v>https://s.shopee.co.th/7AayMA6qAc</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1088,37 +1088,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>【New Arrival】Gaabor หม้อทอดไร้น้ำมัน 12L 1600W โต้ะสองชั้น 12เมนูอัจฉริยะ หน้าจอสัมผัส บานหน้าต่างมองเห็นได้</v>
+        <v>แอร์เคลื่อนที่ All-in-one 1.5P/16000BTU แอร์ขนาดเล็ก Air mobile เย็นเร็ว เสียงเบา แอร์เคลื่อนที่ เย็น แอร์แบบเคลื่อนที่</v>
       </c>
       <c r="C19" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-moov1hhfvev59b.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mojjzh3j0g0fa4.webp</v>
       </c>
       <c r="D19" t="str">
-        <v>2199.00</v>
+        <v>4989.00</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="G19" t="str">
-        <v>ขายได้ 63 ชิ้น</v>
+        <v>ขายได้ 1พัน+ ชิ้น</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>https://shopee.co.th/product/0/42130137883</v>
+        <v>https://shopee.co.th/product/0/40810864683</v>
       </c>
       <c r="J19" t="str">
-        <v>https://s.shopee.co.th/qgkl2RI3T</v>
+        <v>https://s.shopee.co.th/6py7xYLn1c</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1126,37 +1126,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>TV Direct - SANSHIRO พัดลมอุตสาหกรรม 20" FS-20 5 ใบพัด</v>
+        <v>Toshiba TV 32E31RP ทีวี 32 นิ้ว HD Wifi รุ่น Dolby Audio Smart TV</v>
       </c>
       <c r="C20" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-ma3vs5aezunic4.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mp3edjfh1rt8bb.webp</v>
       </c>
       <c r="D20" t="str">
-        <v>1770.00</v>
+        <v>4990.00</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" t="str">
-        <v>ขายได้ 3พัน+ ชิ้น</v>
+        <v>ขายได้ 10พัน+ ชิ้น</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>https://shopee.co.th/product/0/28481166419</v>
+        <v>https://shopee.co.th/product/0/16240990580</v>
       </c>
       <c r="J20" t="str">
-        <v>https://s.shopee.co.th/4AxCjAOdZq</v>
+        <v>https://s.shopee.co.th/8ATVY0QGlp</v>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1164,31 +1164,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>พัดลมไร้สาย 10/12 นิ้ว MASARU SCFP-900 SCFP-910 มีไฟในตัว พัดลมตั้งแคมป์ พัดลมพกพา พัดลมไฟฟ้า</v>
+        <v>SHARP เครื่องฟอกอากาศ รุ่น FP-J30TA/B สีขาว-ดำ</v>
       </c>
       <c r="C21" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134211-81ztj-mfw4d9mrfnka63.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-8261b-mm8xye7fj94xe2.webp</v>
       </c>
       <c r="D21" t="str">
-        <v>1044.00</v>
+        <v>4190.00</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>35</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>ขายได้ 347 ชิ้น</v>
+        <v>ขายได้ 207 ชิ้น</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>https://shopee.co.th/product/0/26923992754</v>
+        <v>https://shopee.co.th/product/0/20591023137</v>
       </c>
       <c r="J21" t="str">
-        <v>https://s.shopee.co.th/5q5QiEPVjB</v>
+        <v>https://s.shopee.co.th/9Uyt8STEkC</v>
       </c>
       <c r="K21" t="str">
         <v/>
